--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_revive/lang_revive__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_revive/lang_revive__ui__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Bạn đã bị hạ gục</t>
+          <t>Bạn Đã Bị Hạ Gục</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Bạn sắp ngất đi, lần sau hãy cẩn thận hơn.</t>
+          <t>Bạn sắp ngất đi rồi, lần sau hãy cẩn thận hơn nhé.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Bạn đã bị hạ gục</t>
+          <t>Bạn Đã Bị Hạ Gục</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Bạn sắp ngất đi, lần sau hãy cẩn thận hơn.</t>
+          <t>Bạn sắp ngất đi rồi, lần sau hãy cẩn thận hơn nhé.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Bạn đã bị hạ gục</t>
+          <t>Bạn Đã Bị Hạ Gục</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Bạn sắp ngất đi, lần sau hãy cẩn thận hơn.</t>
+          <t>Bạn sắp ngất đi rồi, lần sau hãy cẩn thận hơn nhé.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Bạn đã bị hạ gục</t>
+          <t>Bạn Đã Bị Hạ Gục</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Bạn sắp ngất đi, lần sau hãy cẩn thận hơn.</t>
+          <t>Bạn sắp ngất đi rồi, lần sau hãy cẩn thận hơn nhé.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Bạn đã bị hạ gục</t>
+          <t>Bạn Đã Bị Hạ Gục</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Bạn sắp ngất đi, lần sau hãy cẩn thận hơn.</t>
+          <t>Bạn sắp ngất đi rồi, lần sau hãy cẩn thận hơn nhé.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Bạn đã bị hạ gục</t>
+          <t>Bạn Đã Bị Hạ Gục</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Bạn sắp ngất đi, lần sau hãy cẩn thận hơn.</t>
+          <t>Bạn sắp ngất đi rồi, lần sau hãy cẩn thận hơn nhé.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Bạn đã bị hạ gục</t>
+          <t>Bạn Đã Bị Hạ Gục</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Bạn sắp ngất đi, lần sau hãy cẩn thận hơn.</t>
+          <t>Bạn sắp ngất đi rồi, lần sau hãy cẩn thận hơn nhé.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Bạn đã bị hạ gục</t>
+          <t>Bạn Đã Bị Hạ Gục</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Bạn sắp ngất đi, lần sau hãy cẩn thận hơn.</t>
+          <t>Bạn sắp ngất đi rồi, lần sau hãy cẩn thận hơn nhé.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Bạn đã bị hạ gục</t>
+          <t>Bạn Đã Bị Hạ Gục</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Bạn sắp ngất đi, lần sau hãy cẩn thận hơn.</t>
+          <t>Bạn sắp ngất đi rồi, lần sau hãy cẩn thận hơn nhé.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Bạn đã bị hạ gục</t>
+          <t>Bạn Đã Bị Hạ Gục</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Bạn sắp ngất đi, lần sau hãy cẩn thận hơn.</t>
+          <t>Bạn sắp ngất đi rồi, lần sau hãy cẩn thận hơn nhé.</t>
         </is>
       </c>
     </row>
